--- a/data/bulk-upload-points/upload-points-valid.xlsx
+++ b/data/bulk-upload-points/upload-points-valid.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6489CDDF-7F2B-4745-B5AD-D8B73239ADA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4517A2E3-1FB4-4456-B077-EDED092849D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>remark:</t>
   </si>
@@ -23,22 +23,28 @@
     <t>service</t>
   </si>
   <si>
-    <t>TRANSFER_MONEY</t>
-  </si>
-  <si>
-    <t>RECEIVE_MONEY</t>
+    <t>Transfer Money</t>
+  </si>
+  <si>
+    <t>Receive Money</t>
   </si>
   <si>
     <t>channel</t>
   </si>
   <si>
-    <t>MOBILE_BANKING</t>
-  </si>
-  <si>
-    <t>BRANCH</t>
-  </si>
-  <si>
-    <t>no</t>
+    <t>Mobile Banking</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>idType</t>
+  </si>
+  <si>
+    <t>PASSPORT</t>
+  </si>
+  <si>
+    <t>NID</t>
   </si>
   <si>
     <t>cifId</t>
@@ -53,9 +59,6 @@
     <t>phoneNumber</t>
   </si>
   <si>
-    <t>idType</t>
-  </si>
-  <si>
     <t>idNumber</t>
   </si>
   <si>
@@ -77,26 +80,29 @@
     <t>USD</t>
   </si>
   <si>
-    <t>PASSPORT</t>
-  </si>
-  <si>
-    <t>Earn from purchase</t>
-  </si>
-  <si>
-    <t>Panha</t>
-  </si>
-  <si>
-    <t>panha</t>
-  </si>
-  <si>
-    <t>ID0011223ABCD</t>
+    <t>TRX-001</t>
+  </si>
+  <si>
+    <t>XREF-001</t>
+  </si>
+  <si>
+    <t>Earn points</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>096 350 8350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veayor </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,12 +114,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -482,25 +482,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -508,13 +504,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
@@ -522,109 +518,123 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
       <c r="B7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" t="s">
+        <v>18</v>
+      </c>
+      <c r="M9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="B8">
-        <v>1000</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="H10">
+        <v>100545100</v>
+      </c>
+      <c r="I10">
+        <v>7000</v>
+      </c>
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
+      <c r="M10" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="2">
-        <v>9234234</v>
-      </c>
-      <c r="F8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8">
-        <v>7500</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E9" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="F10:F98" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"TRANSFER_MONEY,RECEIVE_MONEY"</formula1>
+  <dataValidations count="3">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Value" error="Please select from dropdown only." sqref="E10:E100" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Transfer Money,Receive Money"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G10:G98" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"MOBILE_BANKING,BRANCH"</formula1>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Value" error="Please select from dropdown only." sqref="F10:F100" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Mobile Banking,Branch"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Value" error="Please select from dropdown only." sqref="G10:G100" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"PASSPORT,NID"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
